--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CB3B6D-1036-4D81-BF42-3BE24C196DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899357AB-148B-46A6-B9E7-EA7E4D1D4099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76575" yWindow="3375" windowWidth="21600" windowHeight="12675" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899357AB-148B-46A6-B9E7-EA7E4D1D4099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F917843A-4FA6-4FFD-8E2D-030A6B8487BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -165,6 +165,18 @@
   </si>
   <si>
     <t>주페이 방문 당시 다운로드 해줬던 버전, 12/19와 차이 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 03. 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260310.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duty 제어 기능 추가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -799,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E8"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -904,6 +916,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="4">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F917843A-4FA6-4FFD-8E2D-030A6B8487BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8190EF75-FC6F-49DF-A3DF-E9CDBF50CF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,6 +177,18 @@
   </si>
   <si>
     <t>Duty 제어 기능 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 04. 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260401.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head -&gt; Tail, Enable Line Delay, ID Check</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +212,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -238,7 +258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,10 +271,16 @@
     <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -811,123 +837,138 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E9"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.58203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B3" s="4">
+      <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="6">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
